--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120335646</v>
+        <v>120335495</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797765</v>
+        <v>797818</v>
       </c>
       <c r="R2" t="n">
-        <v>7368060</v>
+        <v>7367941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,17 +778,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335571</v>
+        <v>120335657</v>
       </c>
       <c r="B3" t="n">
-        <v>91879</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797860</v>
+        <v>797761</v>
       </c>
       <c r="R3" t="n">
-        <v>7367935</v>
+        <v>7368070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,17 +888,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335348</v>
+        <v>120335797</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797748</v>
+        <v>797725</v>
       </c>
       <c r="R4" t="n">
-        <v>7368041</v>
+        <v>7368120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,17 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120335495</v>
+        <v>120335277</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797818</v>
+        <v>797718</v>
       </c>
       <c r="R5" t="n">
-        <v>7367941</v>
+        <v>7368051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,17 +1108,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120335657</v>
+        <v>120335379</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,30 +1131,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797761</v>
+        <v>797765</v>
       </c>
       <c r="R6" t="n">
-        <v>7368070</v>
+        <v>7367970</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,13 +1201,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,17 +1223,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335277</v>
+        <v>120335285</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1246,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1272,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>797718</v>
+        <v>797737</v>
       </c>
       <c r="R7" t="n">
-        <v>7368051</v>
+        <v>7368058</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120335803</v>
+        <v>120335818</v>
       </c>
       <c r="B8" t="n">
-        <v>90742</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,27 +1356,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1382,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>797735</v>
+        <v>797750</v>
       </c>
       <c r="R8" t="n">
-        <v>7368125</v>
+        <v>7368135</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335263</v>
+        <v>120335302</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,30 +1466,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1492,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>797680</v>
+        <v>797740</v>
       </c>
       <c r="R9" t="n">
-        <v>7368060</v>
+        <v>7368050</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,13 +1536,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,17 +1558,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335655</v>
+        <v>120335716</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,25 +1577,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797761</v>
+        <v>797786</v>
       </c>
       <c r="R10" t="n">
-        <v>7368070</v>
+        <v>7368067</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335302</v>
+        <v>120335646</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,31 +1691,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1713,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797740</v>
+        <v>797765</v>
       </c>
       <c r="R11" t="n">
-        <v>7368050</v>
+        <v>7368060</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,17 +1760,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1773,17 +1778,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120335202</v>
+        <v>120335816</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,27 +1801,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1827,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>797710</v>
+        <v>797740</v>
       </c>
       <c r="R12" t="n">
-        <v>7368120</v>
+        <v>7368130</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120335379</v>
+        <v>120335765</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,31 +1911,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1938,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>797765</v>
+        <v>797761</v>
       </c>
       <c r="R13" t="n">
-        <v>7367970</v>
+        <v>7368093</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1982,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,6 +1991,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1998,17 +2003,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120335765</v>
+        <v>120335803</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>90742</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,27 +2026,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2052,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>797761</v>
+        <v>797735</v>
       </c>
       <c r="R14" t="n">
-        <v>7368093</v>
+        <v>7368125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,11 +2095,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2113,17 +2113,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120335751</v>
+        <v>120335655</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2132,25 +2132,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>797740</v>
+        <v>797761</v>
       </c>
       <c r="R15" t="n">
-        <v>7368090</v>
+        <v>7368070</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,17 +2223,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120335351</v>
+        <v>120335591</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,34 +2242,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2277,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>797748</v>
+        <v>797793</v>
       </c>
       <c r="R16" t="n">
-        <v>7368041</v>
+        <v>7368059</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,6 +2312,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2333,17 +2335,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120335816</v>
+        <v>120335263</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,27 +2358,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2387,10 +2389,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>797740</v>
+        <v>797680</v>
       </c>
       <c r="R17" t="n">
-        <v>7368130</v>
+        <v>7368060</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120335716</v>
+        <v>120335751</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2466,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>797786</v>
+        <v>797740</v>
       </c>
       <c r="R18" t="n">
-        <v>7368067</v>
+        <v>7368090</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,17 +2555,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120335285</v>
+        <v>120335257</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,27 +2578,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2607,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>797737</v>
+        <v>797725</v>
       </c>
       <c r="R19" t="n">
-        <v>7368058</v>
+        <v>7368090</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,17 +2665,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120335797</v>
+        <v>120335348</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,21 +2688,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2717,10 +2719,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>797725</v>
+        <v>797748</v>
       </c>
       <c r="R20" t="n">
-        <v>7368120</v>
+        <v>7368041</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,17 +2775,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120335257</v>
+        <v>120335202</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,21 +2798,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>797725</v>
+        <v>797710</v>
       </c>
       <c r="R21" t="n">
-        <v>7368090</v>
+        <v>7368120</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335818</v>
+        <v>120335351</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2906,21 +2908,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797750</v>
+        <v>797748</v>
       </c>
       <c r="R22" t="n">
-        <v>7368135</v>
+        <v>7368041</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2993,17 +2995,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335591</v>
+        <v>120335571</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>91879</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3012,31 +3014,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3044,10 +3049,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>797793</v>
+        <v>797860</v>
       </c>
       <c r="R23" t="n">
-        <v>7368059</v>
+        <v>7367935</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,11 +3087,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335657</v>
+        <v>120335277</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797761</v>
+        <v>797718</v>
       </c>
       <c r="R3" t="n">
-        <v>7368070</v>
+        <v>7368051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,14 +888,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335797</v>
+        <v>120335657</v>
       </c>
       <c r="B4" t="n">
         <v>90580</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797725</v>
+        <v>797761</v>
       </c>
       <c r="R4" t="n">
-        <v>7368120</v>
+        <v>7368070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,17 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120335277</v>
+        <v>120335797</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,27 +1021,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797718</v>
+        <v>797725</v>
       </c>
       <c r="R5" t="n">
-        <v>7368051</v>
+        <v>7368120</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335302</v>
+        <v>120335716</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,31 +1466,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1498,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>797740</v>
+        <v>797786</v>
       </c>
       <c r="R9" t="n">
-        <v>7368050</v>
+        <v>7368067</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,17 +1535,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1558,17 +1553,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335716</v>
+        <v>120335302</v>
       </c>
       <c r="B10" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,30 +1576,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1612,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797786</v>
+        <v>797740</v>
       </c>
       <c r="R10" t="n">
-        <v>7368067</v>
+        <v>7368050</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,13 +1646,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120335495</v>
+        <v>120335716</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797818</v>
+        <v>797786</v>
       </c>
       <c r="R2" t="n">
-        <v>7367941</v>
+        <v>7368067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335277</v>
+        <v>120335351</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797718</v>
+        <v>797748</v>
       </c>
       <c r="R3" t="n">
-        <v>7368051</v>
+        <v>7368041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,17 +888,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335657</v>
+        <v>120335818</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,27 +911,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797761</v>
+        <v>797750</v>
       </c>
       <c r="R4" t="n">
-        <v>7368070</v>
+        <v>7368135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120335379</v>
+        <v>120335655</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,35 +1127,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797765</v>
+        <v>797761</v>
       </c>
       <c r="R6" t="n">
-        <v>7367970</v>
+        <v>7368070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,17 +1200,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,14 +1218,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335285</v>
+        <v>120335657</v>
       </c>
       <c r="B7" t="n">
         <v>90580</v>
@@ -1277,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>797737</v>
+        <v>797761</v>
       </c>
       <c r="R7" t="n">
-        <v>7368058</v>
+        <v>7368070</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,17 +1328,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120335818</v>
+        <v>120335348</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,27 +1351,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1387,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>797750</v>
+        <v>797748</v>
       </c>
       <c r="R8" t="n">
-        <v>7368135</v>
+        <v>7368041</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,17 +1438,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335716</v>
+        <v>120335263</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,27 +1461,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1497,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>797786</v>
+        <v>797680</v>
       </c>
       <c r="R9" t="n">
-        <v>7368067</v>
+        <v>7368060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,17 +1548,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335302</v>
+        <v>120335571</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>91879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,35 +1567,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1608,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797740</v>
+        <v>797860</v>
       </c>
       <c r="R10" t="n">
-        <v>7368050</v>
+        <v>7367935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,17 +1640,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1668,17 +1658,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335646</v>
+        <v>120335765</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,27 +1681,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1722,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797765</v>
+        <v>797761</v>
       </c>
       <c r="R11" t="n">
-        <v>7368060</v>
+        <v>7368093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,6 +1750,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1778,17 +1773,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120335816</v>
+        <v>120335803</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>90742</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1796,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>797740</v>
+        <v>797735</v>
       </c>
       <c r="R12" t="n">
-        <v>7368130</v>
+        <v>7368125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120335765</v>
+        <v>120335751</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,27 +1906,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1942,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>797761</v>
+        <v>797740</v>
       </c>
       <c r="R13" t="n">
-        <v>7368093</v>
+        <v>7368090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,11 +1975,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2003,17 +1993,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120335803</v>
+        <v>120335495</v>
       </c>
       <c r="B14" t="n">
-        <v>90742</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,27 +2016,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2057,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>797735</v>
+        <v>797818</v>
       </c>
       <c r="R14" t="n">
-        <v>7368125</v>
+        <v>7367941</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,17 +2103,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120335655</v>
+        <v>120335277</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2132,31 +2122,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2167,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>797761</v>
+        <v>797718</v>
       </c>
       <c r="R15" t="n">
-        <v>7368070</v>
+        <v>7368051</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,17 +2213,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120335591</v>
+        <v>120335302</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,31 +2232,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2274,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>797793</v>
+        <v>797740</v>
       </c>
       <c r="R16" t="n">
-        <v>7368059</v>
+        <v>7368050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2308,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,7 +2317,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2335,17 +2328,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120335263</v>
+        <v>120335816</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,27 +2351,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2389,10 +2382,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>797680</v>
+        <v>797740</v>
       </c>
       <c r="R17" t="n">
-        <v>7368060</v>
+        <v>7368130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120335751</v>
+        <v>120335285</v>
       </c>
       <c r="B18" t="n">
         <v>90580</v>
@@ -2499,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>797740</v>
+        <v>797737</v>
       </c>
       <c r="R18" t="n">
-        <v>7368090</v>
+        <v>7368058</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,7 +2548,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2672,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120335348</v>
+        <v>120335646</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2688,21 +2681,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2719,10 +2712,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>797748</v>
+        <v>797765</v>
       </c>
       <c r="R20" t="n">
-        <v>7368041</v>
+        <v>7368060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2775,7 +2768,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2892,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335351</v>
+        <v>120335591</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,34 +2897,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2939,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797748</v>
+        <v>797793</v>
       </c>
       <c r="R22" t="n">
-        <v>7368041</v>
+        <v>7368059</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,6 +2967,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2995,17 +2990,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335571</v>
+        <v>120335379</v>
       </c>
       <c r="B23" t="n">
-        <v>91879</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3014,34 +3009,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3049,10 +3045,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>797860</v>
+        <v>797765</v>
       </c>
       <c r="R23" t="n">
-        <v>7367935</v>
+        <v>7367970</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3087,13 +3083,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120335716</v>
+        <v>120335351</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797786</v>
+        <v>797748</v>
       </c>
       <c r="R2" t="n">
-        <v>7368067</v>
+        <v>7368041</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335351</v>
+        <v>120335818</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797748</v>
+        <v>797750</v>
       </c>
       <c r="R3" t="n">
-        <v>7368041</v>
+        <v>7368135</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,17 +888,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335818</v>
+        <v>120335716</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,27 +911,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797750</v>
+        <v>797786</v>
       </c>
       <c r="R4" t="n">
-        <v>7368135</v>
+        <v>7368067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335571</v>
+        <v>120335765</v>
       </c>
       <c r="B10" t="n">
-        <v>91879</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,31 +1567,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797860</v>
+        <v>797761</v>
       </c>
       <c r="R10" t="n">
-        <v>7367935</v>
+        <v>7368093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,6 +1640,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1658,17 +1663,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335765</v>
+        <v>120335571</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>91879</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,31 +1682,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797761</v>
+        <v>797860</v>
       </c>
       <c r="R11" t="n">
-        <v>7368093</v>
+        <v>7367935</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,11 +1755,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120335351</v>
+        <v>120335591</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797748</v>
+        <v>797793</v>
       </c>
       <c r="R2" t="n">
-        <v>7368041</v>
+        <v>7368059</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +757,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335818</v>
+        <v>120335351</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797750</v>
+        <v>797748</v>
       </c>
       <c r="R3" t="n">
-        <v>7368135</v>
+        <v>7368041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,17 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335716</v>
+        <v>120335655</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797786</v>
+        <v>797761</v>
       </c>
       <c r="R4" t="n">
-        <v>7368067</v>
+        <v>7368070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120335797</v>
+        <v>120335379</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,30 +1023,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797725</v>
+        <v>797765</v>
       </c>
       <c r="R5" t="n">
-        <v>7368120</v>
+        <v>7367970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,13 +1093,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120335655</v>
+        <v>120335716</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797761</v>
+        <v>797786</v>
       </c>
       <c r="R6" t="n">
-        <v>7368070</v>
+        <v>7368067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335657</v>
+        <v>120335285</v>
       </c>
       <c r="B7" t="n">
         <v>90580</v>
@@ -1272,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>797761</v>
+        <v>797737</v>
       </c>
       <c r="R7" t="n">
-        <v>7368070</v>
+        <v>7368058</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,17 +1335,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120335348</v>
+        <v>120335217</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>797748</v>
+        <v>797725</v>
       </c>
       <c r="R8" t="n">
-        <v>7368041</v>
+        <v>7368120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,17 +1445,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335263</v>
+        <v>120335277</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>797680</v>
+        <v>797718</v>
       </c>
       <c r="R9" t="n">
-        <v>7368060</v>
+        <v>7368051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,14 +1555,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335765</v>
+        <v>120335818</v>
       </c>
       <c r="B10" t="n">
         <v>79623</v>
@@ -1602,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797761</v>
+        <v>797750</v>
       </c>
       <c r="R10" t="n">
-        <v>7368093</v>
+        <v>7368135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,11 +1647,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1663,17 +1665,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335571</v>
+        <v>120335495</v>
       </c>
       <c r="B11" t="n">
-        <v>91879</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,31 +1684,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1717,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797860</v>
+        <v>797818</v>
       </c>
       <c r="R11" t="n">
-        <v>7367935</v>
+        <v>7367941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,17 +1775,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120335803</v>
+        <v>120335646</v>
       </c>
       <c r="B12" t="n">
-        <v>90742</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,21 +1798,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>797735</v>
+        <v>797765</v>
       </c>
       <c r="R12" t="n">
-        <v>7368125</v>
+        <v>7368060</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120335751</v>
+        <v>120335816</v>
       </c>
       <c r="B13" t="n">
         <v>90580</v>
@@ -1940,7 +1942,7 @@
         <v>797740</v>
       </c>
       <c r="R13" t="n">
-        <v>7368090</v>
+        <v>7368130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120335495</v>
+        <v>120335257</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,21 +2018,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2047,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>797818</v>
+        <v>797725</v>
       </c>
       <c r="R14" t="n">
-        <v>7367941</v>
+        <v>7368090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,17 +2105,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120335277</v>
+        <v>120335348</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,27 +2128,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2157,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>797718</v>
+        <v>797748</v>
       </c>
       <c r="R15" t="n">
-        <v>7368051</v>
+        <v>7368041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,17 +2215,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120335302</v>
+        <v>120335751</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,31 +2238,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2271,7 +2272,7 @@
         <v>797740</v>
       </c>
       <c r="R16" t="n">
-        <v>7368050</v>
+        <v>7368090</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,17 +2307,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2328,17 +2325,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120335816</v>
+        <v>120335571</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>91879</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,25 +2344,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2382,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>797740</v>
+        <v>797860</v>
       </c>
       <c r="R17" t="n">
-        <v>7368130</v>
+        <v>7367935</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2445,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120335285</v>
+        <v>120335263</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,27 +2458,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2492,10 +2489,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>797737</v>
+        <v>797680</v>
       </c>
       <c r="R18" t="n">
-        <v>7368058</v>
+        <v>7368060</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,14 +2545,14 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120335257</v>
+        <v>120335765</v>
       </c>
       <c r="B19" t="n">
         <v>79623</v>
@@ -2602,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>797725</v>
+        <v>797761</v>
       </c>
       <c r="R19" t="n">
-        <v>7368090</v>
+        <v>7368093</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,6 +2637,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2658,14 +2660,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120335646</v>
+        <v>120335657</v>
       </c>
       <c r="B20" t="n">
         <v>90580</v>
@@ -2712,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>797765</v>
+        <v>797761</v>
       </c>
       <c r="R20" t="n">
-        <v>7368060</v>
+        <v>7368070</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,7 +2770,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2885,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335591</v>
+        <v>120335302</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,31 +2899,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2929,10 +2935,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797793</v>
+        <v>797740</v>
       </c>
       <c r="R22" t="n">
-        <v>7368059</v>
+        <v>7368050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2969,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,7 +2984,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2990,17 +2995,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335379</v>
+        <v>120335803</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,31 +3018,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3045,10 +3049,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>797765</v>
+        <v>797735</v>
       </c>
       <c r="R23" t="n">
-        <v>7367970</v>
+        <v>7368125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3083,17 +3087,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120335591</v>
+        <v>120335495</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797793</v>
+        <v>797818</v>
       </c>
       <c r="R2" t="n">
-        <v>7368059</v>
+        <v>7367941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +760,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,17 +778,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335351</v>
+        <v>120335285</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,27 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -834,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797748</v>
+        <v>797737</v>
       </c>
       <c r="R3" t="n">
-        <v>7368041</v>
+        <v>7368058</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,17 +888,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335655</v>
+        <v>120335797</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797761</v>
+        <v>797725</v>
       </c>
       <c r="R4" t="n">
-        <v>7368070</v>
+        <v>7368120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,17 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120335379</v>
+        <v>120335202</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,31 +1021,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797765</v>
+        <v>797710</v>
       </c>
       <c r="R5" t="n">
-        <v>7367970</v>
+        <v>7368120</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,17 +1090,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120335716</v>
+        <v>120335818</v>
       </c>
       <c r="B6" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,27 +1131,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1169,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797786</v>
+        <v>797750</v>
       </c>
       <c r="R6" t="n">
-        <v>7368067</v>
+        <v>7368135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,14 +1218,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335285</v>
+        <v>120335657</v>
       </c>
       <c r="B7" t="n">
         <v>90580</v>
@@ -1279,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>797737</v>
+        <v>797761</v>
       </c>
       <c r="R7" t="n">
-        <v>7368058</v>
+        <v>7368070</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,17 +1328,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120335217</v>
+        <v>120335655</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,25 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>797725</v>
+        <v>797761</v>
       </c>
       <c r="R8" t="n">
-        <v>7368120</v>
+        <v>7368070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,14 +1438,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335277</v>
+        <v>120335257</v>
       </c>
       <c r="B9" t="n">
         <v>79623</v>
@@ -1499,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>797718</v>
+        <v>797725</v>
       </c>
       <c r="R9" t="n">
-        <v>7368051</v>
+        <v>7368090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,17 +1548,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335818</v>
+        <v>120335348</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,27 +1571,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1609,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797750</v>
+        <v>797748</v>
       </c>
       <c r="R10" t="n">
-        <v>7368135</v>
+        <v>7368041</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,17 +1658,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335495</v>
+        <v>120335816</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,27 +1681,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1719,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797818</v>
+        <v>797740</v>
       </c>
       <c r="R11" t="n">
-        <v>7367941</v>
+        <v>7368130</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,17 +1768,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120335646</v>
+        <v>120335302</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,30 +1791,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1829,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>797765</v>
+        <v>797740</v>
       </c>
       <c r="R12" t="n">
-        <v>7368060</v>
+        <v>7368050</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,13 +1861,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1885,17 +1883,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120335816</v>
+        <v>120335765</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,27 +1906,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1939,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>797740</v>
+        <v>797761</v>
       </c>
       <c r="R13" t="n">
-        <v>7368130</v>
+        <v>7368093</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,6 +1975,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1995,17 +1998,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120335257</v>
+        <v>120335646</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,27 +2021,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2049,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>797725</v>
+        <v>797765</v>
       </c>
       <c r="R14" t="n">
-        <v>7368090</v>
+        <v>7368060</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2112,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120335348</v>
+        <v>120335803</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>90742</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2159,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>797748</v>
+        <v>797735</v>
       </c>
       <c r="R15" t="n">
-        <v>7368041</v>
+        <v>7368125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,17 +2218,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120335751</v>
+        <v>120335379</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,30 +2241,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2269,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>797740</v>
+        <v>797765</v>
       </c>
       <c r="R16" t="n">
-        <v>7368090</v>
+        <v>7367970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,13 +2311,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2332,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120335571</v>
+        <v>120335351</v>
       </c>
       <c r="B17" t="n">
-        <v>91879</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,31 +2352,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2379,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>797860</v>
+        <v>797748</v>
       </c>
       <c r="R17" t="n">
-        <v>7367935</v>
+        <v>7368041</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2443,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2552,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120335765</v>
+        <v>120335571</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>91879</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,31 +2572,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2599,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>797761</v>
+        <v>797860</v>
       </c>
       <c r="R19" t="n">
-        <v>7368093</v>
+        <v>7367935</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,11 +2645,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2660,17 +2663,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120335657</v>
+        <v>120335277</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,27 +2686,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2714,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>797761</v>
+        <v>797718</v>
       </c>
       <c r="R20" t="n">
-        <v>7368070</v>
+        <v>7368051</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,17 +2773,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120335202</v>
+        <v>120335591</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2789,34 +2792,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>797710</v>
+        <v>797793</v>
       </c>
       <c r="R21" t="n">
-        <v>7368120</v>
+        <v>7368059</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,6 +2862,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2880,17 +2885,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335302</v>
+        <v>120335716</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2903,31 +2908,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2935,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797740</v>
+        <v>797786</v>
       </c>
       <c r="R22" t="n">
-        <v>7368050</v>
+        <v>7368067</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2973,17 +2977,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335803</v>
+        <v>120335751</v>
       </c>
       <c r="B23" t="n">
-        <v>90742</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>797735</v>
+        <v>797740</v>
       </c>
       <c r="R23" t="n">
-        <v>7368125</v>
+        <v>7368090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120335495</v>
+        <v>120335657</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797818</v>
+        <v>797761</v>
       </c>
       <c r="R2" t="n">
-        <v>7367941</v>
+        <v>7368070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335285</v>
+        <v>120335571</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>91879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797737</v>
+        <v>797860</v>
       </c>
       <c r="R3" t="n">
-        <v>7368058</v>
+        <v>7367935</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,17 +888,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335797</v>
+        <v>120335202</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,27 +911,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797725</v>
+        <v>797710</v>
       </c>
       <c r="R4" t="n">
         <v>7368120</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120335202</v>
+        <v>120335217</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,27 +1021,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797710</v>
+        <v>797725</v>
       </c>
       <c r="R5" t="n">
         <v>7368120</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120335818</v>
+        <v>120335803</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>90742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,27 +1131,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797750</v>
+        <v>797735</v>
       </c>
       <c r="R6" t="n">
-        <v>7368135</v>
+        <v>7368125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335657</v>
+        <v>120335495</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>797761</v>
+        <v>797818</v>
       </c>
       <c r="R7" t="n">
-        <v>7368070</v>
+        <v>7367941</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120335655</v>
+        <v>120335263</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,31 +1347,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>797761</v>
+        <v>797680</v>
       </c>
       <c r="R8" t="n">
-        <v>7368070</v>
+        <v>7368060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,17 +1438,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335257</v>
+        <v>120335646</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,27 +1461,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>797725</v>
+        <v>797765</v>
       </c>
       <c r="R9" t="n">
-        <v>7368090</v>
+        <v>7368060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335348</v>
+        <v>120335655</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,25 +1567,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797748</v>
+        <v>797761</v>
       </c>
       <c r="R10" t="n">
-        <v>7368041</v>
+        <v>7368070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335816</v>
+        <v>120335379</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,30 +1681,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1712,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797740</v>
+        <v>797765</v>
       </c>
       <c r="R11" t="n">
-        <v>7368130</v>
+        <v>7367970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,13 +1751,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1775,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120335302</v>
+        <v>120335285</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,31 +1796,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1823,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>797740</v>
+        <v>797737</v>
       </c>
       <c r="R12" t="n">
-        <v>7368050</v>
+        <v>7368058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,17 +1865,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,14 +1883,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120335765</v>
+        <v>120335257</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>797761</v>
+        <v>797725</v>
       </c>
       <c r="R13" t="n">
-        <v>7368093</v>
+        <v>7368090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,11 +1975,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,17 +1993,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120335646</v>
+        <v>120335277</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,27 +2016,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2052,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>797765</v>
+        <v>797718</v>
       </c>
       <c r="R14" t="n">
-        <v>7368060</v>
+        <v>7368051</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,17 +2103,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120335803</v>
+        <v>120335591</v>
       </c>
       <c r="B15" t="n">
-        <v>90742</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,34 +2122,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>797735</v>
+        <v>797793</v>
       </c>
       <c r="R15" t="n">
-        <v>7368125</v>
+        <v>7368059</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,6 +2192,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2218,17 +2215,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120335379</v>
+        <v>120335818</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,31 +2238,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2273,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>797765</v>
+        <v>797750</v>
       </c>
       <c r="R16" t="n">
-        <v>7367970</v>
+        <v>7368135</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,17 +2307,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2450,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120335263</v>
+        <v>120335716</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2466,27 +2458,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2497,10 +2489,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>797680</v>
+        <v>797786</v>
       </c>
       <c r="R18" t="n">
-        <v>7368060</v>
+        <v>7368067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,17 +2545,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120335571</v>
+        <v>120335751</v>
       </c>
       <c r="B19" t="n">
-        <v>91879</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2572,25 +2564,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>797860</v>
+        <v>797740</v>
       </c>
       <c r="R19" t="n">
-        <v>7367935</v>
+        <v>7368090</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120335277</v>
+        <v>120335816</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,27 +2678,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2717,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>797718</v>
+        <v>797740</v>
       </c>
       <c r="R20" t="n">
-        <v>7368051</v>
+        <v>7368130</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,17 +2765,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120335591</v>
+        <v>120335348</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,31 +2784,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2824,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>797793</v>
+        <v>797748</v>
       </c>
       <c r="R21" t="n">
-        <v>7368059</v>
+        <v>7368041</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,11 +2857,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2885,17 +2875,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335716</v>
+        <v>120335765</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,27 +2898,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2939,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797786</v>
+        <v>797761</v>
       </c>
       <c r="R22" t="n">
-        <v>7368067</v>
+        <v>7368093</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,6 +2967,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2995,17 +2990,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335751</v>
+        <v>120335302</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3018,30 +3013,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3052,7 +3048,7 @@
         <v>797740</v>
       </c>
       <c r="R23" t="n">
-        <v>7368090</v>
+        <v>7368050</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3087,13 +3083,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120335818</v>
+        <v>120335751</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,27 +2238,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>797750</v>
+        <v>797740</v>
       </c>
       <c r="R16" t="n">
-        <v>7368135</v>
+        <v>7368090</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120335716</v>
+        <v>120335818</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,27 +2458,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>797786</v>
+        <v>797750</v>
       </c>
       <c r="R18" t="n">
-        <v>7368067</v>
+        <v>7368135</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,17 +2545,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120335751</v>
+        <v>120335716</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>797740</v>
+        <v>797786</v>
       </c>
       <c r="R19" t="n">
-        <v>7368090</v>
+        <v>7368067</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335765</v>
+        <v>120335302</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,30 +2898,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2929,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797761</v>
+        <v>797740</v>
       </c>
       <c r="R22" t="n">
-        <v>7368093</v>
+        <v>7368050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2969,7 +2970,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,7 +2979,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2990,17 +2990,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335302</v>
+        <v>120335765</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,31 +3013,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3045,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>797740</v>
+        <v>797761</v>
       </c>
       <c r="R23" t="n">
-        <v>7368050</v>
+        <v>7368093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3085,7 +3084,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,6 +3093,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120335657</v>
+        <v>120335263</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797761</v>
+        <v>797680</v>
       </c>
       <c r="R2" t="n">
-        <v>7368070</v>
+        <v>7368060</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,17 +778,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335571</v>
+        <v>120335285</v>
       </c>
       <c r="B3" t="n">
-        <v>91879</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797860</v>
+        <v>797737</v>
       </c>
       <c r="R3" t="n">
-        <v>7367935</v>
+        <v>7368058</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,17 +888,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335202</v>
+        <v>120335655</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,31 +907,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797710</v>
+        <v>797761</v>
       </c>
       <c r="R4" t="n">
-        <v>7368120</v>
+        <v>7368070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,17 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120335217</v>
+        <v>120335379</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,30 +1021,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797725</v>
+        <v>797765</v>
       </c>
       <c r="R5" t="n">
-        <v>7368120</v>
+        <v>7367970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,13 +1091,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120335803</v>
+        <v>120335591</v>
       </c>
       <c r="B6" t="n">
-        <v>90742</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,34 +1132,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797735</v>
+        <v>797793</v>
       </c>
       <c r="R6" t="n">
-        <v>7368125</v>
+        <v>7368059</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,6 +1202,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1218,14 +1225,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335495</v>
+        <v>120335351</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1272,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>797818</v>
+        <v>797748</v>
       </c>
       <c r="R7" t="n">
-        <v>7367941</v>
+        <v>7368041</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120335263</v>
+        <v>120335716</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,27 +1358,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1382,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>797680</v>
+        <v>797786</v>
       </c>
       <c r="R8" t="n">
-        <v>7368060</v>
+        <v>7368067</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,17 +1445,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335646</v>
+        <v>120335818</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,27 +1468,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1492,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>797765</v>
+        <v>797750</v>
       </c>
       <c r="R9" t="n">
-        <v>7368060</v>
+        <v>7368135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335655</v>
+        <v>120335765</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,31 +1574,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1605,7 +1612,7 @@
         <v>797761</v>
       </c>
       <c r="R10" t="n">
-        <v>7368070</v>
+        <v>7368093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,6 +1647,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1658,17 +1670,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335379</v>
+        <v>120335803</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,31 +1693,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1713,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797765</v>
+        <v>797735</v>
       </c>
       <c r="R11" t="n">
-        <v>7367970</v>
+        <v>7368125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,17 +1762,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1780,7 +1787,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120335285</v>
+        <v>120335751</v>
       </c>
       <c r="B12" t="n">
         <v>90580</v>
@@ -1827,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>797737</v>
+        <v>797740</v>
       </c>
       <c r="R12" t="n">
-        <v>7368058</v>
+        <v>7368090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,17 +1890,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120335257</v>
+        <v>120335797</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,27 +1913,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1940,7 +1947,7 @@
         <v>797725</v>
       </c>
       <c r="R13" t="n">
-        <v>7368090</v>
+        <v>7368120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120335277</v>
+        <v>120335657</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,27 +2023,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2047,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>797718</v>
+        <v>797761</v>
       </c>
       <c r="R14" t="n">
-        <v>7368051</v>
+        <v>7368070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,17 +2110,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120335591</v>
+        <v>120335646</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,31 +2129,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2154,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>797793</v>
+        <v>797765</v>
       </c>
       <c r="R15" t="n">
-        <v>7368059</v>
+        <v>7368060</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,11 +2202,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2215,17 +2220,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120335751</v>
+        <v>120335571</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>91879</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,25 +2239,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>797740</v>
+        <v>797860</v>
       </c>
       <c r="R16" t="n">
-        <v>7368090</v>
+        <v>7367935</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120335351</v>
+        <v>120335257</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,21 +2353,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2379,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>797748</v>
+        <v>797725</v>
       </c>
       <c r="R17" t="n">
-        <v>7368041</v>
+        <v>7368090</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,17 +2440,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120335818</v>
+        <v>120335202</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,21 +2463,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>797750</v>
+        <v>797710</v>
       </c>
       <c r="R18" t="n">
-        <v>7368135</v>
+        <v>7368120</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120335716</v>
+        <v>120335495</v>
       </c>
       <c r="B19" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,27 +2573,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2599,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>797786</v>
+        <v>797818</v>
       </c>
       <c r="R19" t="n">
-        <v>7368067</v>
+        <v>7367941</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120335348</v>
+        <v>120335302</v>
       </c>
       <c r="B21" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,30 +2793,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2819,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>797748</v>
+        <v>797740</v>
       </c>
       <c r="R21" t="n">
-        <v>7368041</v>
+        <v>7368050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,13 +2863,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2875,17 +2885,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335302</v>
+        <v>120335348</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,31 +2908,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2930,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797740</v>
+        <v>797748</v>
       </c>
       <c r="R22" t="n">
-        <v>7368050</v>
+        <v>7368041</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,17 +2977,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2990,14 +2995,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335765</v>
+        <v>120335277</v>
       </c>
       <c r="B23" t="n">
         <v>79623</v>
@@ -3044,10 +3049,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>797761</v>
+        <v>797718</v>
       </c>
       <c r="R23" t="n">
-        <v>7368093</v>
+        <v>7368051</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,11 +3087,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120335263</v>
+        <v>120335803</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797680</v>
+        <v>797735</v>
       </c>
       <c r="R2" t="n">
-        <v>7368060</v>
+        <v>7368125</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120335285</v>
+        <v>120335765</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797737</v>
+        <v>797761</v>
       </c>
       <c r="R3" t="n">
-        <v>7368058</v>
+        <v>7368093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt på stammen av en urgammal jättebjörk!</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,17 +893,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren, Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120335655</v>
+        <v>120335263</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,31 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -942,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797761</v>
+        <v>797680</v>
       </c>
       <c r="R4" t="n">
-        <v>7368070</v>
+        <v>7368060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,17 +1003,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120335379</v>
+        <v>120335495</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,31 +1026,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797765</v>
+        <v>797818</v>
       </c>
       <c r="R5" t="n">
-        <v>7367970</v>
+        <v>7367941</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,17 +1095,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120335591</v>
+        <v>120335257</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,31 +1132,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797793</v>
+        <v>797725</v>
       </c>
       <c r="R6" t="n">
-        <v>7368059</v>
+        <v>7368090</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,11 +1205,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1225,17 +1223,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335351</v>
+        <v>120335751</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,27 +1246,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1279,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>797748</v>
+        <v>797740</v>
       </c>
       <c r="R7" t="n">
-        <v>7368041</v>
+        <v>7368090</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,17 +1333,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120335716</v>
+        <v>120335655</v>
       </c>
       <c r="B8" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,25 +1352,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>797786</v>
+        <v>797761</v>
       </c>
       <c r="R8" t="n">
-        <v>7368067</v>
+        <v>7368070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335818</v>
+        <v>120335379</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,30 +1466,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1499,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>797750</v>
+        <v>797765</v>
       </c>
       <c r="R9" t="n">
-        <v>7368135</v>
+        <v>7367970</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,13 +1536,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1562,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335765</v>
+        <v>120335571</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>91879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,31 +1577,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1609,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797761</v>
+        <v>797860</v>
       </c>
       <c r="R10" t="n">
-        <v>7368093</v>
+        <v>7367935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,11 +1650,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>rikligt på stammen av en urgammal jättebjörk!</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1670,17 +1668,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Kristina  Berglund</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335803</v>
+        <v>120335716</v>
       </c>
       <c r="B11" t="n">
-        <v>90742</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,21 +1691,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1724,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797735</v>
+        <v>797786</v>
       </c>
       <c r="R11" t="n">
-        <v>7368125</v>
+        <v>7368067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,17 +1778,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120335751</v>
+        <v>120335202</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,27 +1801,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1834,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>797740</v>
+        <v>797710</v>
       </c>
       <c r="R12" t="n">
-        <v>7368090</v>
+        <v>7368120</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1895,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120335797</v>
+        <v>120335217</v>
       </c>
       <c r="B13" t="n">
         <v>90580</v>
@@ -2007,7 +2005,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120335657</v>
+        <v>120335646</v>
       </c>
       <c r="B14" t="n">
         <v>90580</v>
@@ -2054,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>797761</v>
+        <v>797765</v>
       </c>
       <c r="R14" t="n">
-        <v>7368070</v>
+        <v>7368060</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,14 +2108,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120335646</v>
+        <v>120335285</v>
       </c>
       <c r="B15" t="n">
         <v>90580</v>
@@ -2164,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>797765</v>
+        <v>797737</v>
       </c>
       <c r="R15" t="n">
-        <v>7368060</v>
+        <v>7368058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,17 +2218,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120335571</v>
+        <v>120335657</v>
       </c>
       <c r="B16" t="n">
-        <v>91879</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,25 +2237,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2274,10 +2272,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>797860</v>
+        <v>797761</v>
       </c>
       <c r="R16" t="n">
-        <v>7367935</v>
+        <v>7368070</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,14 +2328,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120335257</v>
+        <v>120335818</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2384,10 +2382,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>797725</v>
+        <v>797750</v>
       </c>
       <c r="R17" t="n">
-        <v>7368090</v>
+        <v>7368135</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120335202</v>
+        <v>120335277</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,21 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2494,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>797710</v>
+        <v>797718</v>
       </c>
       <c r="R18" t="n">
-        <v>7368120</v>
+        <v>7368051</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2550,17 +2548,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120335495</v>
+        <v>120335302</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2573,30 +2571,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2604,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>797818</v>
+        <v>797740</v>
       </c>
       <c r="R19" t="n">
-        <v>7367941</v>
+        <v>7368050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2642,13 +2641,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2660,17 +2663,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120335816</v>
+        <v>120335351</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,27 +2686,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2714,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>797740</v>
+        <v>797748</v>
       </c>
       <c r="R20" t="n">
-        <v>7368130</v>
+        <v>7368041</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,17 +2773,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120335302</v>
+        <v>120335816</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,31 +2796,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,7 +2830,7 @@
         <v>797740</v>
       </c>
       <c r="R21" t="n">
-        <v>7368050</v>
+        <v>7368130</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2863,17 +2865,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2885,17 +2883,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335348</v>
+        <v>120335591</v>
       </c>
       <c r="B22" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,34 +2902,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2939,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797748</v>
+        <v>797793</v>
       </c>
       <c r="R22" t="n">
-        <v>7368041</v>
+        <v>7368059</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,6 +2972,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335277</v>
+        <v>120335348</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3018,27 +3018,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>797718</v>
+        <v>797748</v>
       </c>
       <c r="R23" t="n">
-        <v>7368051</v>
+        <v>7368041</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -1565,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120335571</v>
+        <v>120335716</v>
       </c>
       <c r="B10" t="n">
-        <v>91879</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,25 +1577,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>797860</v>
+        <v>797786</v>
       </c>
       <c r="R10" t="n">
-        <v>7367935</v>
+        <v>7368067</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120335716</v>
+        <v>120335571</v>
       </c>
       <c r="B11" t="n">
-        <v>90864</v>
+        <v>91879</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,25 +1687,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>797786</v>
+        <v>797860</v>
       </c>
       <c r="R11" t="n">
-        <v>7368067</v>
+        <v>7367935</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120335591</v>
+        <v>120335348</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2902,31 +2902,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2934,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>797793</v>
+        <v>797748</v>
       </c>
       <c r="R22" t="n">
-        <v>7368059</v>
+        <v>7368041</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2972,11 +2975,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2995,17 +2993,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120335348</v>
+        <v>120335591</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3014,34 +3012,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3049,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>797748</v>
+        <v>797793</v>
       </c>
       <c r="R23" t="n">
-        <v>7368041</v>
+        <v>7368059</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3087,6 +3082,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Kristina  Berglund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3110,6 +3110,142 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121466360</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bredheden1, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>797730</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7368114</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>bäckskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3115,7 +3115,7 @@
         <v>121466360</v>
       </c>
       <c r="B24" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3115,7 +3115,7 @@
         <v>121466360</v>
       </c>
       <c r="B24" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3115,7 +3115,7 @@
         <v>121466360</v>
       </c>
       <c r="B24" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3115,7 +3115,7 @@
         <v>121466360</v>
       </c>
       <c r="B24" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -1668,11 +1668,11 @@
         <v>120335655</v>
       </c>
       <c r="B11" t="n">
-        <v>91081</v>
+        <v>91168</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3115,7 +3115,7 @@
         <v>121466360</v>
       </c>
       <c r="B24" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>121988870</v>
       </c>
       <c r="B26" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>121988861</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>122232494</v>
       </c>
       <c r="B28" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>122260297</v>
       </c>
       <c r="B29" t="n">
-        <v>91065</v>
+        <v>91075</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3384,7 +3384,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121988870</v>
+        <v>121988861</v>
       </c>
       <c r="B26" t="n">
         <v>79727</v>
@@ -3423,14 +3423,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>bredheden4, Nb</t>
+          <t>bredheden5, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>797722</v>
+        <v>797758</v>
       </c>
       <c r="R26" t="n">
-        <v>7368053</v>
+        <v>7368091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,19 +3480,29 @@
           <t>Blandskog</t>
         </is>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>bäckskog</t>
+        </is>
+      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>gammal,grov</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula # gammal,grov</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3510,7 +3520,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121988861</v>
+        <v>121988870</v>
       </c>
       <c r="B27" t="n">
         <v>79727</v>
@@ -3549,14 +3559,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>bredheden5, Nb</t>
+          <t>bredheden4, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>797758</v>
+        <v>797722</v>
       </c>
       <c r="R27" t="n">
-        <v>7368091</v>
+        <v>7368053</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,29 +3616,19 @@
           <t>Blandskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>bäckskog</t>
-        </is>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>gammal,grov</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Betula # gammal,grov</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3251,7 +3251,7 @@
         <v>121972530</v>
       </c>
       <c r="B25" t="n">
-        <v>74739</v>
+        <v>74744</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>121988861</v>
       </c>
       <c r="B26" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>121988870</v>
       </c>
       <c r="B27" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>122232494</v>
       </c>
       <c r="B28" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>122260297</v>
       </c>
       <c r="B29" t="n">
-        <v>91075</v>
+        <v>91087</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90789</v>
+        <v>90801</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3649,7 +3649,7 @@
         <v>122232494</v>
       </c>
       <c r="B28" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>122260297</v>
       </c>
       <c r="B29" t="n">
-        <v>91087</v>
+        <v>91092</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90801</v>
+        <v>90808</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3649,7 +3649,7 @@
         <v>122232494</v>
       </c>
       <c r="B28" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3663,11 +3663,6 @@
       </c>
       <c r="E28" t="n">
         <v>220787</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
         <v>122260297</v>
       </c>
       <c r="B29" t="n">
-        <v>91092</v>
+        <v>91097</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3775,11 +3770,6 @@
       </c>
       <c r="E29" t="n">
         <v>658</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3859,11 +3849,6 @@
           <t>bäckskog</t>
         </is>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3897,7 +3882,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90808</v>
+        <v>90813</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,11 +3896,6 @@
       </c>
       <c r="E30" t="n">
         <v>1202</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3993,11 +3973,6 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>bäckskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3649,7 +3649,7 @@
         <v>122232494</v>
       </c>
       <c r="B28" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3663,6 +3663,11 @@
       </c>
       <c r="E28" t="n">
         <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3756,7 +3761,7 @@
         <v>122260297</v>
       </c>
       <c r="B29" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,6 +3775,11 @@
       </c>
       <c r="E29" t="n">
         <v>658</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3849,6 +3859,11 @@
           <t>bäckskog</t>
         </is>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3882,7 +3897,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90813</v>
+        <v>90826</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,6 +3911,11 @@
       </c>
       <c r="E30" t="n">
         <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3973,6 +3993,11 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>bäckskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3649,7 +3649,7 @@
         <v>122232494</v>
       </c>
       <c r="B28" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>122260297</v>
       </c>
       <c r="B29" t="n">
-        <v>91110</v>
+        <v>91123</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3649,7 +3649,7 @@
         <v>122232494</v>
       </c>
       <c r="B28" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>122260297</v>
       </c>
       <c r="B29" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3761,7 +3761,7 @@
         <v>122260297</v>
       </c>
       <c r="B29" t="n">
-        <v>91124</v>
+        <v>91125</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2024 artfynd.xlsx
+++ b/artfynd/A 33908-2024 artfynd.xlsx
@@ -3897,7 +3897,7 @@
         <v>122347972</v>
       </c>
       <c r="B30" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
